--- a/repair/back/doc/estimate/periodic2.xlsx
+++ b/repair/back/doc/estimate/periodic2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="7" lowestEdited="7" rupBuild=""/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="731" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="731" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="갑지" sheetId="21" r:id="rId1"/>
@@ -373,7 +373,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="267">
   <si>
     <t>식</t>
   </si>
@@ -1886,6 +1886,12 @@
   <si>
     <t xml:space="preserve">다. 점 검 범 위  : </t>
   </si>
+  <si>
+    <t>동법 시행령 제8조에 따라</t>
+  </si>
+  <si>
+    <t>「시설물의 안전 및 유지관리에 관한 특별법」(이하 “시설물안전법”이라 한다) 제11조, 제12조 및</t>
+  </si>
 </sst>
 </file>
 
@@ -1963,7 +1969,7 @@
     <numFmt numFmtId="243" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="244" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;;@"/>
   </numFmts>
-  <fonts count="138">
+  <fonts count="145">
     <font>
       <sz val="11.0"/>
       <name val="돋움"/>
@@ -2633,12 +2639,6 @@
       <color rgb="FFFA7D00"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="돋움"/>
-      <color theme="1"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <name val="돋움"/>
       <color rgb="FF006100"/>
@@ -2707,6 +2707,52 @@
       <b/>
       <sz val="32.0"/>
       <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="20.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.0"/>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24.0"/>
+      <name val="바탕"/>
       <color rgb="FF000000"/>
     </font>
   </fonts>
@@ -4113,7 +4159,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4122,7 +4167,6 @@
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4131,7 +4175,6 @@
       <bottom style="thick">
         <color rgb="FFACCCEA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4140,7 +4183,6 @@
       <bottom style="medium">
         <color theme="4" tint="0.399980"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -4155,7 +4197,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -4170,7 +4211,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -4185,7 +4225,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4194,7 +4233,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4205,7 +4243,6 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3161">
@@ -13647,19 +13684,19 @@
     <xf numFmtId="0" fontId="123" fillId="0" borderId="108" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="109" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="109" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13668,10 +13705,10 @@
     <xf numFmtId="0" fontId="110" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="127" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13680,10 +13717,10 @@
     <xf numFmtId="0" fontId="110" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="127" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13692,10 +13729,10 @@
     <xf numFmtId="0" fontId="110" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="127" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13704,10 +13741,10 @@
     <xf numFmtId="0" fontId="110" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="33" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="34" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="127" fillId="33" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="34" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="35" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13716,10 +13753,10 @@
     <xf numFmtId="0" fontId="110" fillId="36" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="37" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="38" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="127" fillId="37" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="38" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="39" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13728,14 +13765,14 @@
     <xf numFmtId="0" fontId="110" fillId="40" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="41" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="127" fillId="41" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="390">
+  <cellXfs count="397">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
@@ -14897,6 +14934,27 @@
     </xf>
     <xf numFmtId="37" fontId="105" fillId="0" borderId="0" xfId="3112" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3162">
@@ -18835,7 +18893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C1:AH1594"/>
+  <dimension ref="C1:AF1594"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="13.500000"/>
   <cols>
     <col min="1" max="3" style="90" width="8.78277800" customWidth="1" outlineLevel="0"/>
@@ -18844,11 +18902,10 @@
     <col min="13" max="31" style="90" width="3.33833334" customWidth="1" outlineLevel="0"/>
     <col min="32" max="32" style="90" width="2.33833334" customWidth="1" outlineLevel="0"/>
     <col min="33" max="259" style="90" width="6.78277800" customWidth="1" outlineLevel="0"/>
-    <col min="260" max="260" style="90" width="8.78277800" customWidth="1" outlineLevel="0"/>
-    <col min="261" max="16384" style="90" width="8.78277800" customWidth="1" outlineLevel="0"/>
+    <col min="260" max="16384" style="90" width="8.78277800" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:34" s="96" customFormat="1" ht="42.000000" customHeight="1">
+    <row r="1" spans="3:31" s="96" customFormat="1" ht="42.000000" customHeight="1">
       <c r="C1" s="137"/>
       <c r="D1" s="337" t="s">
         <v>85</v>
@@ -18881,7 +18938,7 @@
       <c r="AD1" s="337"/>
       <c r="AE1" s="337"/>
     </row>
-    <row r="2" spans="3:34" s="96" customFormat="1" ht="12.000000" customHeight="1">
+    <row r="2" spans="3:31" s="96" customFormat="1" ht="12.000000" customHeight="1">
       <c r="C2" s="137"/>
       <c r="D2" s="137"/>
       <c r="E2" s="137"/>
@@ -18912,7 +18969,7 @@
       <c r="AD2" s="138"/>
       <c r="AE2" s="138"/>
     </row>
-    <row r="3" spans="3:34" s="96" customFormat="1" ht="18.000000" customHeight="1">
+    <row r="3" spans="3:31" s="96" customFormat="1" ht="18.000000" customHeight="1">
       <c r="C3" s="137"/>
       <c r="D3" s="338" t="s">
         <v>187</v>
@@ -18945,7 +19002,7 @@
       <c r="AD3" s="338"/>
       <c r="AE3" s="338"/>
     </row>
-    <row r="4" spans="3:34" s="96" customFormat="1" ht="7.500000" customHeight="1">
+    <row r="4" spans="3:31" s="96" customFormat="1" ht="7.500000" customHeight="1">
       <c r="C4" s="137"/>
       <c r="D4" s="139"/>
       <c r="E4" s="139"/>
@@ -18976,7 +19033,7 @@
       <c r="AD4" s="140"/>
       <c r="AE4" s="140"/>
     </row>
-    <row r="5" spans="3:34" s="96" customFormat="1" ht="5.000000" customHeight="1">
+    <row r="5" spans="3:31" s="96" customFormat="1" ht="5.000000" customHeight="1">
       <c r="C5" s="137"/>
       <c r="D5" s="137"/>
       <c r="E5" s="137"/>
@@ -19007,7 +19064,7 @@
       <c r="AD5" s="138"/>
       <c r="AE5" s="138"/>
     </row>
-    <row r="6" spans="3:34" s="96" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="6" spans="3:31" s="96" customFormat="1" ht="20.000000" customHeight="1">
       <c r="C6" s="137"/>
       <c r="D6" s="145" t="s">
         <v>84</v>
@@ -19042,7 +19099,7 @@
       <c r="AD6" s="137"/>
       <c r="AE6" s="137"/>
     </row>
-    <row r="7" spans="3:34" s="96" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="7" spans="3:31" s="96" customFormat="1" ht="20.000000" customHeight="1">
       <c r="C7" s="137"/>
       <c r="D7" s="145" t="s">
         <v>82</v>
@@ -19077,7 +19134,7 @@
       <c r="AD7" s="137"/>
       <c r="AE7" s="137"/>
     </row>
-    <row r="8" spans="3:34" s="96" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="8" spans="3:31" s="96" customFormat="1" ht="20.000000" customHeight="1">
       <c r="C8" s="137"/>
       <c r="D8" s="145" t="s">
         <v>81</v>
@@ -19112,7 +19169,7 @@
       <c r="AD8" s="336"/>
       <c r="AE8" s="336"/>
     </row>
-    <row r="9" spans="3:34" s="96" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="9" spans="3:31" s="96" customFormat="1" ht="20.000000" customHeight="1">
       <c r="C9" s="137"/>
       <c r="D9" s="145" t="s">
         <v>80</v>
@@ -19125,32 +19182,8 @@
       </c>
       <c r="I9" s="141"/>
       <c r="J9" s="141"/>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
-      <c r="M9" s="96"/>
-      <c r="N9" s="96"/>
-      <c r="O9" s="96"/>
-      <c r="P9" s="96"/>
-      <c r="Q9" s="96"/>
-      <c r="R9" s="96"/>
-      <c r="S9" s="96"/>
-      <c r="T9" s="96"/>
-      <c r="U9" s="96"/>
-      <c r="V9" s="96"/>
-      <c r="W9" s="96"/>
-      <c r="X9" s="96"/>
-      <c r="Y9" s="96"/>
-      <c r="Z9" s="96"/>
-      <c r="AA9" s="96"/>
-      <c r="AB9" s="96"/>
-      <c r="AC9" s="96"/>
-      <c r="AD9" s="96"/>
-      <c r="AE9" s="96"/>
-      <c r="AF9" s="96"/>
-      <c r="AG9" s="96"/>
-      <c r="AH9" s="96"/>
-    </row>
-    <row r="10" spans="3:34" s="96" customFormat="1" ht="20.000000" customHeight="1">
+    </row>
+    <row r="10" spans="3:31" s="96" customFormat="1" ht="20.000000" customHeight="1">
       <c r="C10" s="137"/>
       <c r="D10" s="145" t="s">
         <v>78</v>
@@ -19185,7 +19218,7 @@
       <c r="AD10" s="336"/>
       <c r="AE10" s="336"/>
     </row>
-    <row r="11" spans="3:34" s="96" customFormat="1" ht="13.500000" hidden="1" customHeight="1">
+    <row r="11" spans="3:31" s="96" customFormat="1" ht="13.500000" hidden="1" customHeight="1">
       <c r="C11" s="137"/>
       <c r="D11" s="142"/>
       <c r="E11" s="142"/>
@@ -19216,7 +19249,7 @@
       <c r="AD11" s="142"/>
       <c r="AE11" s="142"/>
     </row>
-    <row r="12" spans="3:34" s="96" customFormat="1" ht="7.500000" customHeight="1">
+    <row r="12" spans="3:31" s="96" customFormat="1" ht="7.500000" customHeight="1">
       <c r="C12" s="137"/>
       <c r="D12" s="139"/>
       <c r="E12" s="139"/>
@@ -19247,7 +19280,7 @@
       <c r="AD12" s="139"/>
       <c r="AE12" s="139"/>
     </row>
-    <row r="13" spans="3:34" s="96" customFormat="1" ht="5.000000" customHeight="1">
+    <row r="13" spans="3:31" s="96" customFormat="1" ht="5.000000" customHeight="1">
       <c r="C13" s="137"/>
       <c r="D13" s="137"/>
       <c r="E13" s="137"/>
@@ -19278,7 +19311,7 @@
       <c r="AD13" s="137"/>
       <c r="AE13" s="137"/>
     </row>
-    <row r="14" spans="3:34" s="96" customFormat="1" ht="16.000000" customHeight="1">
+    <row r="14" spans="3:31" s="96" customFormat="1" ht="16.000000" customHeight="1">
       <c r="C14" s="137"/>
       <c r="D14" s="328" t="s">
         <v>246</v>
@@ -19311,7 +19344,7 @@
       <c r="AD14" s="328"/>
       <c r="AE14" s="328"/>
     </row>
-    <row r="15" spans="3:34" s="96" customFormat="1" ht="10.000000" customHeight="1">
+    <row r="15" spans="3:31" s="96" customFormat="1" ht="10.000000" customHeight="1">
       <c r="C15" s="137"/>
       <c r="D15" s="137"/>
       <c r="E15" s="137"/>
@@ -19342,7 +19375,7 @@
       <c r="AD15" s="137"/>
       <c r="AE15" s="137"/>
     </row>
-    <row r="16" spans="3:34" s="96" customFormat="1" ht="70.000000" customHeight="1">
+    <row r="16" spans="3:31" s="96" customFormat="1" ht="70.000000" customHeight="1">
       <c r="C16" s="137"/>
       <c r="D16" s="143" t="s">
         <v>247</v>
@@ -34275,10 +34308,10 @@
     <mergeCell ref="D20:M20"/>
     <mergeCell ref="H21:M21"/>
     <mergeCell ref="N21:AE21"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:AE22"/>
     <mergeCell ref="H23:M23"/>
     <mergeCell ref="N23:AE23"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:AE22"/>
     <mergeCell ref="H24:M24"/>
     <mergeCell ref="N24:AE24"/>
     <mergeCell ref="H25:M25"/>
@@ -34387,9 +34420,9 @@
         <v>72</v>
       </c>
       <c r="C5" s="366"/>
-      <c r="D5" s="367" t="e">
+      <c r="D5" s="367">
         <f>"일금 "&amp;NUMBERSTRING(H30,1)&amp;"원정"&amp;TEXT(H30,"(￦ #,##0)")&amp;" "</f>
-        <v>일금 #VALUE!원정</v>
+        <v/>
       </c>
       <c r="E5" s="367"/>
       <c r="F5" s="367"/>
@@ -36307,7 +36340,7 @@
     </row>
     <row r="60" spans="2:21" ht="24.950000" customHeight="1">
       <c r="B60" s="115" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="C60" s="115"/>
       <c r="D60" s="115"/>
@@ -36330,25 +36363,25 @@
       <c r="U60" s="115"/>
     </row>
     <row r="61" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B61" s="246" t="s">
-        <v>241</v>
-      </c>
-      <c r="C61" s="246"/>
-      <c r="D61" s="246"/>
-      <c r="E61" s="246"/>
-      <c r="F61" s="246"/>
-      <c r="G61" s="246"/>
-      <c r="H61" s="246"/>
-      <c r="I61" s="246"/>
-      <c r="J61" s="247" t="str">
+      <c r="B61" s="393" t="s">
+        <v>265</v>
+      </c>
+      <c r="C61" s="393"/>
+      <c r="D61" s="393"/>
+      <c r="E61" s="393"/>
+      <c r="F61" s="393"/>
+      <c r="G61" s="393"/>
+      <c r="H61" s="393"/>
+      <c r="I61" s="396" t="str">
         <f>B9</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="K61" s="247"/>
-      <c r="L61" s="247"/>
-      <c r="M61" s="247"/>
-      <c r="N61" s="247"/>
-      <c r="O61" s="247"/>
+      <c r="J61" s="396"/>
+      <c r="K61" s="396"/>
+      <c r="L61" s="396"/>
+      <c r="M61" s="396"/>
+      <c r="N61" s="396"/>
+      <c r="O61" s="396"/>
       <c r="P61" s="248" t="s">
         <v>243</v>
       </c>
@@ -36485,7 +36518,7 @@
     </row>
     <row r="69" spans="2:21" ht="20.000000" customHeight="1">
       <c r="C69" s="115" t="str">
-        <f>"② 위      치 : "&amp;E55</f>
+        <f>"② 위      치 : "&amp;갑지!N22</f>
         <v>② 위      치 : 인천 계양구 아나지로 199 (효성동)</v>
       </c>
       <c r="D69" s="115"/>
@@ -38607,8 +38640,8 @@
     <mergeCell ref="B57:U57"/>
     <mergeCell ref="B58:U58"/>
     <mergeCell ref="B60:U60"/>
-    <mergeCell ref="B61:I61"/>
-    <mergeCell ref="J61:O61"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="I61:O61"/>
     <mergeCell ref="P61:U61"/>
     <mergeCell ref="B62:U62"/>
     <mergeCell ref="B64:J64"/>

--- a/repair/back/doc/estimate/periodic2.xlsx
+++ b/repair/back/doc/estimate/periodic2.xlsx
@@ -1969,7 +1969,7 @@
     <numFmt numFmtId="243" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="244" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;;@"/>
   </numFmts>
-  <fonts count="145">
+  <fonts count="148">
     <font>
       <sz val="11.0"/>
       <name val="돋움"/>
@@ -2753,6 +2753,22 @@
       <b/>
       <sz val="24.0"/>
       <name val="바탕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="8.0"/>
+      <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
   </fonts>
@@ -35054,8 +35070,8 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait"/>
   <colBreaks count="2" manualBreakCount="2">
+    <brk id="9" max="1048575" man="1"/>
     <brk id="9" max="36" man="1"/>
-    <brk id="9" max="1048575" man="1"/>
   </colBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -38176,8 +38192,8 @@
       </c>
       <c r="Q147" s="88"/>
       <c r="R147" s="181">
-        <f>R138*P147%</f>
-        <v>109268.6</v>
+        <f>ROUND(R138*P147%,0)</f>
+        <v>109269</v>
       </c>
       <c r="S147" s="181"/>
       <c r="T147" s="181"/>
@@ -38210,8 +38226,8 @@
       </c>
       <c r="Q148" s="88"/>
       <c r="R148" s="164">
-        <f>(R138+R147)*P148%</f>
-        <v>120195.46</v>
+        <f>ROUND((R138+R147)*P148%,0)</f>
+        <v>120196</v>
       </c>
       <c r="S148" s="164"/>
       <c r="T148" s="164"/>
@@ -38237,7 +38253,7 @@
       <c r="P149" s="80"/>
       <c r="Q149" s="80"/>
       <c r="R149" s="176">
-        <f>SUM(R151:R155)</f>
+        <f>INT(SUM(R151:R155))</f>
         <v>219268</v>
       </c>
       <c r="S149" s="176"/>
@@ -38448,7 +38464,7 @@
       <c r="Q157" s="88"/>
       <c r="R157" s="166">
         <f>R138+R147+R148+R149</f>
-        <v>1541418.06</v>
+        <v>1541419</v>
       </c>
       <c r="S157" s="166"/>
       <c r="T157" s="166"/>
